--- a/Settings/Chocolatey/Chocolatey.xlsx
+++ b/Settings/Chocolatey/Chocolatey.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10209"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl$\Ubuntu-22.04\home\markus\projects\wiki\Settings\Chocolatey\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/markus/Projects/wiki/Settings/Chocolatey/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0599A668-A925-462F-961A-AFA385865243}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E8707F4-FEBD-C74D-90D8-7D3B6DE25F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38310" yWindow="0" windowWidth="19380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34120" yWindow="500" windowWidth="34140" windowHeight="42700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chocolatey" sheetId="1" r:id="rId1"/>
@@ -73,7 +73,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="756" uniqueCount="425">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="427">
   <si>
     <t>adblockpluschrome</t>
   </si>
@@ -1371,6 +1371,12 @@
   </si>
   <si>
     <t>Obsidian.Obsidian</t>
+  </si>
+  <si>
+    <t>BetterDisplay</t>
+  </si>
+  <si>
+    <t>Steuerung der Monitor-Lautstärke</t>
   </si>
 </sst>
 </file>
@@ -1887,17 +1893,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H139"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="26.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="6.1796875" customWidth="1"/>
-    <col min="4" max="4" width="6.453125" customWidth="1"/>
-    <col min="5" max="6" width="7.6328125" customWidth="1"/>
-    <col min="7" max="7" width="30.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="70.6328125" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="6.1640625" customWidth="1"/>
+    <col min="4" max="4" width="6.5" customWidth="1"/>
+    <col min="5" max="6" width="7.6640625" customWidth="1"/>
+    <col min="7" max="7" width="30.5" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="70.6640625" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>54</v>
       </c>
@@ -1923,7 +1929,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>58</v>
       </c>
@@ -1947,7 +1953,7 @@
       </c>
       <c r="H2" s="7"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -1963,7 +1969,7 @@
       <c r="G3" s="13"/>
       <c r="H3" s="13"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>59</v>
       </c>
@@ -1989,7 +1995,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>1</v>
       </c>
@@ -2003,7 +2009,7 @@
       </c>
       <c r="H5" s="7"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>91</v>
       </c>
@@ -2019,7 +2025,7 @@
       </c>
       <c r="H6" s="7"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>92</v>
       </c>
@@ -2033,7 +2039,7 @@
       <c r="G7" s="6"/>
       <c r="H7" s="7"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>93</v>
       </c>
@@ -2047,7 +2053,7 @@
       <c r="G8" s="6"/>
       <c r="H8" s="7"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>60</v>
       </c>
@@ -2067,7 +2073,7 @@
       </c>
       <c r="H9" s="7"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="10" t="s">
         <v>100</v>
       </c>
@@ -2081,7 +2087,7 @@
       </c>
       <c r="H10" s="7"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>2</v>
       </c>
@@ -2093,7 +2099,7 @@
       <c r="G11" s="6"/>
       <c r="H11" s="7"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
         <v>114</v>
       </c>
@@ -2109,7 +2115,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>124</v>
       </c>
@@ -2123,7 +2129,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>125</v>
       </c>
@@ -2137,7 +2143,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="9" t="s">
         <v>3</v>
       </c>
@@ -2153,7 +2159,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>138</v>
       </c>
@@ -2169,7 +2175,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>4</v>
       </c>
@@ -2181,7 +2187,7 @@
       <c r="G17" s="6"/>
       <c r="H17" s="7"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>5</v>
       </c>
@@ -2195,7 +2201,7 @@
       </c>
       <c r="H18" s="7"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
         <v>101</v>
       </c>
@@ -2211,7 +2217,7 @@
       </c>
       <c r="H19" s="7"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
         <v>140</v>
       </c>
@@ -2229,7 +2235,7 @@
       </c>
       <c r="H20" s="7"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
         <v>133</v>
       </c>
@@ -2245,7 +2251,7 @@
       </c>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
         <v>173</v>
       </c>
@@ -2263,7 +2269,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="10" t="s">
         <v>6</v>
       </c>
@@ -2279,7 +2285,7 @@
       <c r="G23" s="6"/>
       <c r="H23" s="7"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
         <v>7</v>
       </c>
@@ -2291,7 +2297,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="7"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
         <v>102</v>
       </c>
@@ -2309,7 +2315,7 @@
       </c>
       <c r="H25" s="7"/>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
         <v>99</v>
       </c>
@@ -2327,7 +2333,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
         <v>8</v>
       </c>
@@ -2347,7 +2353,7 @@
       </c>
       <c r="H27" s="7"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1" t="s">
         <v>150</v>
       </c>
@@ -2369,7 +2375,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="10" t="s">
         <v>116</v>
       </c>
@@ -2387,7 +2393,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1" t="s">
         <v>9</v>
       </c>
@@ -2407,7 +2413,7 @@
       </c>
       <c r="H30" s="7"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1" t="s">
         <v>10</v>
       </c>
@@ -2429,7 +2435,7 @@
       </c>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1" t="s">
         <v>111</v>
       </c>
@@ -2449,7 +2455,7 @@
       </c>
       <c r="H32" s="7"/>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1" t="s">
         <v>67</v>
       </c>
@@ -2465,7 +2471,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="10" t="s">
         <v>56</v>
       </c>
@@ -2483,7 +2489,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="10" t="s">
         <v>103</v>
       </c>
@@ -2499,7 +2505,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1" t="s">
         <v>61</v>
       </c>
@@ -2517,7 +2523,7 @@
       </c>
       <c r="H36" s="7"/>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>11</v>
       </c>
@@ -2531,7 +2537,7 @@
       </c>
       <c r="H37" s="7"/>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="9" t="s">
         <v>87</v>
       </c>
@@ -2551,7 +2557,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>12</v>
       </c>
@@ -2573,7 +2579,7 @@
       </c>
       <c r="H39" s="7"/>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>13</v>
       </c>
@@ -2591,7 +2597,7 @@
       </c>
       <c r="H40" s="7"/>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>14</v>
       </c>
@@ -2603,7 +2609,7 @@
       <c r="G41" s="6"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>134</v>
       </c>
@@ -2619,7 +2625,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="10" t="s">
         <v>84</v>
       </c>
@@ -2633,7 +2639,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>15</v>
       </c>
@@ -2649,7 +2655,7 @@
       </c>
       <c r="H44" s="7"/>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="12" t="s">
         <v>149</v>
       </c>
@@ -2669,7 +2675,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>16</v>
       </c>
@@ -2691,7 +2697,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>90</v>
       </c>
@@ -2711,7 +2717,7 @@
       </c>
       <c r="H47" s="7"/>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="9" t="s">
         <v>96</v>
       </c>
@@ -2729,7 +2735,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>80</v>
       </c>
@@ -2747,7 +2753,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>17</v>
       </c>
@@ -2763,7 +2769,7 @@
       </c>
       <c r="H50" s="7"/>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>18</v>
       </c>
@@ -2779,7 +2785,7 @@
       <c r="G51" s="6"/>
       <c r="H51" s="7"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>161</v>
       </c>
@@ -2797,7 +2803,7 @@
       </c>
       <c r="H52" s="7"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="10" t="s">
         <v>19</v>
       </c>
@@ -2811,7 +2817,7 @@
       </c>
       <c r="H53" s="7"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>20</v>
       </c>
@@ -2833,7 +2839,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>62</v>
       </c>
@@ -2853,7 +2859,7 @@
       </c>
       <c r="H55" s="7"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>162</v>
       </c>
@@ -2875,7 +2881,7 @@
       </c>
       <c r="H56" s="7"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>21</v>
       </c>
@@ -2893,7 +2899,7 @@
       <c r="G57" s="6"/>
       <c r="H57" s="7"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>86</v>
       </c>
@@ -2913,7 +2919,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="10" t="s">
         <v>22</v>
       </c>
@@ -2925,7 +2931,7 @@
       <c r="G59" s="6"/>
       <c r="H59" s="7"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>136</v>
       </c>
@@ -2939,7 +2945,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>122</v>
       </c>
@@ -2955,7 +2961,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="3" t="s">
         <v>55</v>
@@ -2971,7 +2977,7 @@
       </c>
       <c r="H62" s="7"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1" t="s">
         <v>77</v>
       </c>
@@ -2987,7 +2993,7 @@
       </c>
       <c r="H63" s="7"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>230</v>
       </c>
@@ -3005,7 +3011,7 @@
       </c>
       <c r="H64" s="7"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>23</v>
       </c>
@@ -3019,7 +3025,7 @@
       <c r="G65" s="6"/>
       <c r="H65" s="7"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>105</v>
       </c>
@@ -3035,7 +3041,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>141</v>
       </c>
@@ -3051,7 +3057,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>24</v>
       </c>
@@ -3065,7 +3071,7 @@
       </c>
       <c r="H68" s="7"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>25</v>
       </c>
@@ -3079,7 +3085,7 @@
       </c>
       <c r="H69" s="7"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>26</v>
       </c>
@@ -3097,7 +3103,7 @@
       </c>
       <c r="H70" s="7"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>108</v>
       </c>
@@ -3113,7 +3119,7 @@
       </c>
       <c r="H71" s="7"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>109</v>
       </c>
@@ -3129,7 +3135,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>76</v>
       </c>
@@ -3147,7 +3153,7 @@
       </c>
       <c r="H73" s="7"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>81</v>
       </c>
@@ -3161,7 +3167,7 @@
       </c>
       <c r="H74" s="7"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="10" t="s">
         <v>178</v>
       </c>
@@ -3177,7 +3183,7 @@
       </c>
       <c r="H75" s="7"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>27</v>
       </c>
@@ -3195,7 +3201,7 @@
       </c>
       <c r="H76" s="7"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>63</v>
       </c>
@@ -3211,7 +3217,7 @@
       </c>
       <c r="H77" s="7"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>64</v>
       </c>
@@ -3235,7 +3241,7 @@
       </c>
       <c r="H78" s="7"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>69</v>
       </c>
@@ -3253,7 +3259,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -3267,7 +3273,7 @@
       </c>
       <c r="H80" s="7"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3281,7 +3287,7 @@
       </c>
       <c r="H81" s="7"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>95</v>
       </c>
@@ -3295,7 +3301,7 @@
       <c r="G82" s="6"/>
       <c r="H82" s="7"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1" t="s">
         <v>148</v>
       </c>
@@ -3309,7 +3315,7 @@
       </c>
       <c r="H83" s="7"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1" t="s">
         <v>29</v>
       </c>
@@ -3323,7 +3329,7 @@
       </c>
       <c r="H84" s="7"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1" t="s">
         <v>30</v>
       </c>
@@ -3339,7 +3345,7 @@
       </c>
       <c r="H85" s="7"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1" t="s">
         <v>31</v>
       </c>
@@ -3353,7 +3359,7 @@
       </c>
       <c r="H86" s="7"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1" t="s">
         <v>179</v>
       </c>
@@ -3371,7 +3377,7 @@
       </c>
       <c r="H87" s="7"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1" t="s">
         <v>107</v>
       </c>
@@ -3393,7 +3399,7 @@
       </c>
       <c r="H88" s="7"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1" t="s">
         <v>32</v>
       </c>
@@ -3411,7 +3417,7 @@
       </c>
       <c r="H89" s="7"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1" t="s">
         <v>33</v>
       </c>
@@ -3429,7 +3435,7 @@
       </c>
       <c r="H90" s="7"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1" t="s">
         <v>65</v>
       </c>
@@ -3443,7 +3449,7 @@
       </c>
       <c r="H91" s="7"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1" t="s">
         <v>94</v>
       </c>
@@ -3459,7 +3465,7 @@
       </c>
       <c r="H92" s="7"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="10" t="s">
         <v>118</v>
       </c>
@@ -3477,7 +3483,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1" t="s">
         <v>144</v>
       </c>
@@ -3495,7 +3501,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1" t="s">
         <v>78</v>
       </c>
@@ -3511,7 +3517,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1" t="s">
         <v>163</v>
       </c>
@@ -3529,7 +3535,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1" t="s">
         <v>83</v>
       </c>
@@ -3543,7 +3549,7 @@
       </c>
       <c r="H97" s="7"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1" t="s">
         <v>82</v>
       </c>
@@ -3555,7 +3561,7 @@
       <c r="G98" s="6"/>
       <c r="H98" s="7"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1" t="s">
         <v>34</v>
       </c>
@@ -3571,7 +3577,7 @@
       </c>
       <c r="H99" s="7"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1" t="s">
         <v>35</v>
       </c>
@@ -3585,7 +3591,7 @@
       </c>
       <c r="H100" s="7"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1" t="s">
         <v>287</v>
       </c>
@@ -3601,7 +3607,7 @@
       </c>
       <c r="H101" s="7"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="10" t="s">
         <v>120</v>
       </c>
@@ -3619,7 +3625,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1" t="s">
         <v>36</v>
       </c>
@@ -3637,7 +3643,7 @@
       </c>
       <c r="H103" s="7"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1" t="s">
         <v>37</v>
       </c>
@@ -3651,7 +3657,7 @@
       </c>
       <c r="H104" s="7"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1" t="s">
         <v>155</v>
       </c>
@@ -3667,7 +3673,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1" t="s">
         <v>38</v>
       </c>
@@ -3685,7 +3691,7 @@
       </c>
       <c r="H106" s="7"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1" t="s">
         <v>39</v>
       </c>
@@ -3703,7 +3709,7 @@
       </c>
       <c r="H107" s="7"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1" t="s">
         <v>171</v>
       </c>
@@ -3721,7 +3727,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1" t="s">
         <v>172</v>
       </c>
@@ -3739,7 +3745,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1" t="s">
         <v>167</v>
       </c>
@@ -3759,7 +3765,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1" t="s">
         <v>40</v>
       </c>
@@ -3775,7 +3781,7 @@
       </c>
       <c r="H111" s="7"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1" t="s">
         <v>41</v>
       </c>
@@ -3789,7 +3795,7 @@
       </c>
       <c r="H112" s="7"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1" t="s">
         <v>68</v>
       </c>
@@ -3803,7 +3809,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="9" t="s">
         <v>128</v>
       </c>
@@ -3815,7 +3821,7 @@
       <c r="G114" s="6"/>
       <c r="H114" s="7"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1" t="s">
         <v>74</v>
       </c>
@@ -3837,7 +3843,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="10" t="s">
         <v>88</v>
       </c>
@@ -3855,7 +3861,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1" t="s">
         <v>42</v>
       </c>
@@ -3871,7 +3877,7 @@
       <c r="G117" s="6"/>
       <c r="H117" s="7"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1" t="s">
         <v>43</v>
       </c>
@@ -3889,7 +3895,7 @@
       </c>
       <c r="H118" s="7"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1" t="s">
         <v>44</v>
       </c>
@@ -3903,7 +3909,7 @@
       </c>
       <c r="H119" s="7"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1" t="s">
         <v>45</v>
       </c>
@@ -3917,7 +3923,7 @@
       </c>
       <c r="H120" s="7"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1" t="s">
         <v>46</v>
       </c>
@@ -3939,7 +3945,7 @@
       </c>
       <c r="H121" s="7"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1" t="s">
         <v>110</v>
       </c>
@@ -3955,7 +3961,7 @@
       </c>
       <c r="H122" s="7"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1" t="s">
         <v>47</v>
       </c>
@@ -3975,7 +3981,7 @@
       </c>
       <c r="H123" s="7"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1" t="s">
         <v>48</v>
       </c>
@@ -3989,7 +3995,7 @@
       </c>
       <c r="H124" s="7"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1" t="s">
         <v>165</v>
       </c>
@@ -4005,7 +4011,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1" t="s">
         <v>73</v>
       </c>
@@ -4023,7 +4029,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1" t="s">
         <v>49</v>
       </c>
@@ -4047,7 +4053,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1" t="s">
         <v>50</v>
       </c>
@@ -4067,7 +4073,7 @@
       </c>
       <c r="H128" s="7"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1" t="s">
         <v>51</v>
       </c>
@@ -4085,7 +4091,7 @@
       </c>
       <c r="H129" s="7"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1" t="s">
         <v>112</v>
       </c>
@@ -4099,7 +4105,7 @@
       </c>
       <c r="H130" s="7"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="8" t="s">
         <v>127</v>
       </c>
@@ -4111,7 +4117,7 @@
       <c r="G131" s="6"/>
       <c r="H131" s="7"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1" t="s">
         <v>66</v>
       </c>
@@ -4127,7 +4133,7 @@
       </c>
       <c r="H132" s="7"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1" t="s">
         <v>52</v>
       </c>
@@ -4143,7 +4149,7 @@
       <c r="G133" s="6"/>
       <c r="H133" s="7"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="10" t="s">
         <v>53</v>
       </c>
@@ -4161,7 +4167,7 @@
       </c>
       <c r="H134" s="7"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1" t="s">
         <v>113</v>
       </c>
@@ -4181,17 +4187,17 @@
       </c>
       <c r="H135" s="7"/>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="10" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="8" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="9" t="s">
         <v>129</v>
       </c>
@@ -4211,15 +4217,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D44"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="11.453125" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="40.81640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="40.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="22" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="51" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="15" t="s">
         <v>292</v>
       </c>
@@ -4233,7 +4239,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>296</v>
       </c>
@@ -4241,7 +4247,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>297</v>
       </c>
@@ -4255,7 +4261,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>298</v>
       </c>
@@ -4266,7 +4272,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>301</v>
       </c>
@@ -4274,7 +4280,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>302</v>
       </c>
@@ -4288,7 +4294,7 @@
         <v>304</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>305</v>
       </c>
@@ -4296,7 +4302,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>306</v>
       </c>
@@ -4304,7 +4310,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>307</v>
       </c>
@@ -4312,7 +4318,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>308</v>
       </c>
@@ -4320,7 +4326,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>309</v>
       </c>
@@ -4328,7 +4334,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>310</v>
       </c>
@@ -4336,7 +4342,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>311</v>
       </c>
@@ -4344,7 +4350,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>313</v>
       </c>
@@ -4352,7 +4358,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>314</v>
       </c>
@@ -4360,7 +4366,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>315</v>
       </c>
@@ -4368,7 +4374,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>316</v>
       </c>
@@ -4376,7 +4382,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>317</v>
       </c>
@@ -4384,7 +4390,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>318</v>
       </c>
@@ -4392,7 +4398,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>320</v>
       </c>
@@ -4403,7 +4409,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>322</v>
       </c>
@@ -4411,7 +4417,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>323</v>
       </c>
@@ -4419,7 +4425,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>324</v>
       </c>
@@ -4427,7 +4433,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>325</v>
       </c>
@@ -4435,7 +4441,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>326</v>
       </c>
@@ -4443,7 +4449,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>327</v>
       </c>
@@ -4451,7 +4457,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>328</v>
       </c>
@@ -4465,7 +4471,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>331</v>
       </c>
@@ -4473,7 +4479,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>332</v>
       </c>
@@ -4484,7 +4490,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>334</v>
       </c>
@@ -4492,7 +4498,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>335</v>
       </c>
@@ -4500,7 +4506,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>336</v>
       </c>
@@ -4511,7 +4517,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>338</v>
       </c>
@@ -4522,7 +4528,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>339</v>
       </c>
@@ -4533,7 +4539,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>341</v>
       </c>
@@ -4544,7 +4550,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>343</v>
       </c>
@@ -4552,7 +4558,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>344</v>
       </c>
@@ -4560,7 +4566,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>345</v>
       </c>
@@ -4568,7 +4574,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>346</v>
       </c>
@@ -4576,7 +4582,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>347</v>
       </c>
@@ -4584,7 +4590,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>348</v>
       </c>
@@ -4592,7 +4598,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>349</v>
       </c>
@@ -4600,7 +4606,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>350</v>
       </c>
@@ -4608,7 +4614,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>351</v>
       </c>
@@ -4623,15 +4629,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7F93F60-305A-704A-9194-4387AC0BEE7B}">
-  <dimension ref="A1:E49"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:E50"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="17" t="s">
         <v>359</v>
       </c>
@@ -4648,7 +4654,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>325</v>
       </c>
@@ -4659,7 +4665,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>317</v>
       </c>
@@ -4673,7 +4679,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>352</v>
       </c>
@@ -4687,7 +4693,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>354</v>
       </c>
@@ -4701,7 +4707,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>345</v>
       </c>
@@ -4715,7 +4721,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>61</v>
       </c>
@@ -4729,7 +4735,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>394</v>
       </c>
@@ -4743,7 +4749,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>395</v>
       </c>
@@ -4757,7 +4763,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>358</v>
       </c>
@@ -4768,7 +4774,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>396</v>
       </c>
@@ -4782,7 +4788,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>421</v>
       </c>
@@ -4796,7 +4802,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>90</v>
       </c>
@@ -4810,7 +4816,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -4821,7 +4827,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>362</v>
       </c>
@@ -4832,7 +4838,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>39</v>
       </c>
@@ -4843,7 +4849,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>133</v>
       </c>
@@ -4854,7 +4860,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>363</v>
       </c>
@@ -4868,7 +4874,7 @@
         <v>397</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>399</v>
       </c>
@@ -4882,7 +4888,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>398</v>
       </c>
@@ -4893,7 +4899,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>350</v>
       </c>
@@ -4904,7 +4910,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>364</v>
       </c>
@@ -4918,7 +4924,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>365</v>
       </c>
@@ -4932,7 +4938,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>367</v>
       </c>
@@ -4949,7 +4955,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>400</v>
       </c>
@@ -4963,7 +4969,7 @@
         <v>402</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>368</v>
       </c>
@@ -4977,7 +4983,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>403</v>
       </c>
@@ -4991,7 +4997,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>371</v>
       </c>
@@ -5008,7 +5014,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>373</v>
       </c>
@@ -5019,7 +5025,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>374</v>
       </c>
@@ -5033,7 +5039,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>46</v>
       </c>
@@ -5044,7 +5050,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>378</v>
       </c>
@@ -5058,7 +5064,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>381</v>
       </c>
@@ -5072,7 +5078,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>382</v>
       </c>
@@ -5086,7 +5092,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>386</v>
       </c>
@@ -5100,7 +5106,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>380</v>
       </c>
@@ -5111,7 +5117,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>387</v>
       </c>
@@ -5125,7 +5131,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>389</v>
       </c>
@@ -5136,7 +5142,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>390</v>
       </c>
@@ -5150,7 +5156,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>391</v>
       </c>
@@ -5161,7 +5167,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>392</v>
       </c>
@@ -5175,7 +5181,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
         <v>409</v>
       </c>
@@ -5189,7 +5195,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
         <v>410</v>
       </c>
@@ -5200,7 +5206,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A44" t="s">
         <v>411</v>
       </c>
@@ -5211,7 +5217,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A45" t="s">
         <v>413</v>
       </c>
@@ -5225,7 +5231,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
         <v>412</v>
       </c>
@@ -5239,7 +5245,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
         <v>417</v>
       </c>
@@ -5253,17 +5259,31 @@
         <v>418</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="18"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A49" s="18" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>425</v>
+      </c>
+      <c r="B48" t="s">
+        <v>291</v>
+      </c>
+      <c r="C48" t="s">
+        <v>291</v>
+      </c>
+      <c r="D48" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A49" s="18"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A50" s="18" t="s">
         <v>385</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="A49" r:id="rId1" xr:uid="{65CB6B51-C990-C94E-8E20-9886EFDBDD52}"/>
+    <hyperlink ref="A50" r:id="rId1" xr:uid="{65CB6B51-C990-C94E-8E20-9886EFDBDD52}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -5273,18 +5293,18 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065AFD5E-E7C4-4344-BCB5-48CFA86F7E2C}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="63" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>405</v>
       </c>
@@ -5292,17 +5312,17 @@
         <v>406</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>408</v>
       </c>
